--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260918.xlsx
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>146,701,090</t>
+          <t>22,378,317</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>22,378,317</t>
+          <t>146,701,090</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
